--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1923,6 +1923,1042 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121455782</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91137</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vallabrättingens sydsida, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>594412</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6843245</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>relativt gammal barrnaturskog i sydsida</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121455780</v>
+      </c>
+      <c r="B13" t="n">
+        <v>88024</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>510</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vallabrättingens sydsida, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>594412</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6843245</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>relativt gammal barrnaturskog i sydsida</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>1 substratenheter # förrötad klenare granlåga</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121455778</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90983</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>658</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vallabrättingens sydsida, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>594430</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6843492</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121455775</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90717</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vallabrättingens sydsida, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>594314</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6843411</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>bergskrön med gammal hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>1 substratenheter # 400-årig tall med stamsår</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121455776</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vallabrättingens sydsida, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>594238</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6843576</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>relativt gammal grannaturskog i terrängsvacka</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>2 substratenheter # förrötade äldre granlågor</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121455781</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90983</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>658</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vallabrättingens sydsida, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>594412</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6843245</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>relativt gammal barrnaturskog i sydsida</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121455779</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vallabrättingens sydsida, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>594435</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6843227</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>gammal barrnaturskog i sydsida</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121455777</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90983</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>658</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vallabrättingens sydsida, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>594291</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6843506</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>2 substratenheter # förrötade grövre granlågor</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121455774</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79137</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1352</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Småflikig brosklav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ramalina sinensis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vallabrättingens sydsida, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>594327</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6843367</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grenar på fallen äldre asp</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>121455782</v>
       </c>
       <c r="B12" t="n">
-        <v>91137</v>
+        <v>91149</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>121455780</v>
       </c>
       <c r="B13" t="n">
-        <v>88024</v>
+        <v>88031</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121455778</v>
+        <v>121455776</v>
       </c>
       <c r="B14" t="n">
-        <v>90983</v>
+        <v>90709</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2171,21 +2171,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594430</v>
+        <v>594238</v>
       </c>
       <c r="R14" t="n">
-        <v>6843492</v>
+        <v>6843576</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2244,15 +2244,15 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+          <t>relativt gammal grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>2 substratenheter # förrötade äldre granlågor</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121455775</v>
+        <v>121455774</v>
       </c>
       <c r="B15" t="n">
-        <v>90717</v>
+        <v>79140</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>1352</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594314</v>
+        <v>594327</v>
       </c>
       <c r="R15" t="n">
-        <v>6843411</v>
+        <v>6843367</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2354,13 +2354,12 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>bergskrön med gammal hällmarkstallskog</t>
+          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
         </is>
       </c>
       <c r="AN15" t="n">
@@ -2368,7 +2367,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>1 substratenheter # 400-årig tall med stamsår</t>
+          <t>1 substratenheter # grenar på fallen äldre asp</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2386,10 +2385,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121455776</v>
+        <v>121455778</v>
       </c>
       <c r="B16" t="n">
-        <v>90697</v>
+        <v>90995</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2402,21 +2401,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2426,10 +2425,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594238</v>
+        <v>594430</v>
       </c>
       <c r="R16" t="n">
-        <v>6843576</v>
+        <v>6843492</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2475,15 +2474,15 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>relativt gammal grannaturskog i terrängsvacka</t>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade äldre granlågor</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2501,10 +2500,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121455781</v>
+        <v>121455775</v>
       </c>
       <c r="B17" t="n">
-        <v>90983</v>
+        <v>90729</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2517,21 +2516,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2541,10 +2540,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594412</v>
+        <v>594314</v>
       </c>
       <c r="R17" t="n">
-        <v>6843245</v>
+        <v>6843411</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2585,12 +2584,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>bergskrön med gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>1 substratenheter # 400-årig tall med stamsår</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2619,7 +2619,7 @@
         <v>121455779</v>
       </c>
       <c r="B18" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>121455777</v>
       </c>
       <c r="B19" t="n">
-        <v>90983</v>
+        <v>90995</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121455774</v>
+        <v>121455781</v>
       </c>
       <c r="B20" t="n">
-        <v>79137</v>
+        <v>90995</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1352</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594327</v>
+        <v>594412</v>
       </c>
       <c r="R20" t="n">
-        <v>6843367</v>
+        <v>6843245</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>1 substratenheter # grenar på fallen äldre asp</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -1925,10 +1925,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121455782</v>
+        <v>121455774</v>
       </c>
       <c r="B12" t="n">
-        <v>91149</v>
+        <v>79140</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1937,25 +1937,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1352</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594412</v>
+        <v>594327</v>
       </c>
       <c r="R12" t="n">
-        <v>6843245</v>
+        <v>6843367</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
         </is>
       </c>
       <c r="AN12" t="n">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>1 substratenheter # grenar på fallen äldre asp</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121455780</v>
+        <v>121455781</v>
       </c>
       <c r="B13" t="n">
-        <v>88031</v>
+        <v>90996</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad klenare granlåga</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121455776</v>
+        <v>121455778</v>
       </c>
       <c r="B14" t="n">
-        <v>90709</v>
+        <v>90996</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2171,21 +2171,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594238</v>
+        <v>594430</v>
       </c>
       <c r="R14" t="n">
-        <v>6843576</v>
+        <v>6843492</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2244,15 +2244,15 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>relativt gammal grannaturskog i terrängsvacka</t>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade äldre granlågor</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121455774</v>
+        <v>121455780</v>
       </c>
       <c r="B15" t="n">
-        <v>79140</v>
+        <v>88031</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1352</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594327</v>
+        <v>594412</v>
       </c>
       <c r="R15" t="n">
-        <v>6843367</v>
+        <v>6843245</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN15" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>1 substratenheter # grenar på fallen äldre asp</t>
+          <t>1 substratenheter # förrötad klenare granlåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121455778</v>
+        <v>121455782</v>
       </c>
       <c r="B16" t="n">
-        <v>90995</v>
+        <v>91150</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2397,25 +2397,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594430</v>
+        <v>594412</v>
       </c>
       <c r="R16" t="n">
-        <v>6843492</v>
+        <v>6843245</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN16" t="n">
@@ -2503,7 +2503,7 @@
         <v>121455775</v>
       </c>
       <c r="B17" t="n">
-        <v>90729</v>
+        <v>90730</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>121455779</v>
       </c>
       <c r="B18" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>121455777</v>
       </c>
       <c r="B19" t="n">
-        <v>90995</v>
+        <v>90996</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121455781</v>
+        <v>121455776</v>
       </c>
       <c r="B20" t="n">
-        <v>90995</v>
+        <v>90710</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594412</v>
+        <v>594238</v>
       </c>
       <c r="R20" t="n">
-        <v>6843245</v>
+        <v>6843576</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2935,15 +2935,15 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>2 substratenheter # förrötade äldre granlågor</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -1925,10 +1925,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121455774</v>
+        <v>121455780</v>
       </c>
       <c r="B12" t="n">
-        <v>79140</v>
+        <v>88034</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1941,21 +1941,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1352</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594327</v>
+        <v>594412</v>
       </c>
       <c r="R12" t="n">
-        <v>6843367</v>
+        <v>6843245</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN12" t="n">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # grenar på fallen äldre asp</t>
+          <t>1 substratenheter # förrötad klenare granlåga</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121455781</v>
+        <v>121455779</v>
       </c>
       <c r="B13" t="n">
-        <v>90996</v>
+        <v>90713</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594412</v>
+        <v>594435</v>
       </c>
       <c r="R13" t="n">
-        <v>6843245</v>
+        <v>6843227</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN13" t="n">
@@ -2155,10 +2155,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121455778</v>
+        <v>121455782</v>
       </c>
       <c r="B14" t="n">
-        <v>90996</v>
+        <v>91153</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2167,25 +2167,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594430</v>
+        <v>594412</v>
       </c>
       <c r="R14" t="n">
-        <v>6843492</v>
+        <v>6843245</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN14" t="n">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121455780</v>
+        <v>121455775</v>
       </c>
       <c r="B15" t="n">
-        <v>88031</v>
+        <v>90733</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594412</v>
+        <v>594314</v>
       </c>
       <c r="R15" t="n">
-        <v>6843245</v>
+        <v>6843411</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2354,12 +2354,13 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>bergskrön med gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AN15" t="n">
@@ -2367,7 +2368,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad klenare granlåga</t>
+          <t>1 substratenheter # 400-årig tall med stamsår</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2385,10 +2386,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121455782</v>
+        <v>121455774</v>
       </c>
       <c r="B16" t="n">
-        <v>91150</v>
+        <v>79143</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2397,25 +2398,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1352</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2425,10 +2426,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594412</v>
+        <v>594327</v>
       </c>
       <c r="R16" t="n">
-        <v>6843245</v>
+        <v>6843367</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2474,7 +2475,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
         </is>
       </c>
       <c r="AN16" t="n">
@@ -2482,7 +2483,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>1 substratenheter # grenar på fallen äldre asp</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2500,10 +2501,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121455775</v>
+        <v>121455781</v>
       </c>
       <c r="B17" t="n">
-        <v>90730</v>
+        <v>90999</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2516,21 +2517,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2540,10 +2541,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594314</v>
+        <v>594412</v>
       </c>
       <c r="R17" t="n">
-        <v>6843411</v>
+        <v>6843245</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2584,13 +2585,12 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>bergskrön med gammal hällmarkstallskog</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>1 substratenheter # 400-årig tall med stamsår</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121455779</v>
+        <v>121455777</v>
       </c>
       <c r="B18" t="n">
-        <v>90710</v>
+        <v>90999</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594435</v>
+        <v>594291</v>
       </c>
       <c r="R18" t="n">
-        <v>6843227</v>
+        <v>6843506</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2705,15 +2705,15 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>2 substratenheter # förrötade grövre granlågor</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121455777</v>
+        <v>121455776</v>
       </c>
       <c r="B19" t="n">
-        <v>90996</v>
+        <v>90713</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594291</v>
+        <v>594238</v>
       </c>
       <c r="R19" t="n">
-        <v>6843506</v>
+        <v>6843576</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+          <t>relativt gammal grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade grövre granlågor</t>
+          <t>2 substratenheter # förrötade äldre granlågor</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121455776</v>
+        <v>121455778</v>
       </c>
       <c r="B20" t="n">
-        <v>90710</v>
+        <v>90999</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594238</v>
+        <v>594430</v>
       </c>
       <c r="R20" t="n">
-        <v>6843576</v>
+        <v>6843492</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2935,15 +2935,15 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>relativt gammal grannaturskog i terrängsvacka</t>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade äldre granlågor</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -1925,10 +1925,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121455780</v>
+        <v>121455778</v>
       </c>
       <c r="B12" t="n">
-        <v>88034</v>
+        <v>90999</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1941,21 +1941,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594412</v>
+        <v>594430</v>
       </c>
       <c r="R12" t="n">
-        <v>6843245</v>
+        <v>6843492</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN12" t="n">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad klenare granlåga</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121455779</v>
+        <v>121455780</v>
       </c>
       <c r="B13" t="n">
-        <v>90713</v>
+        <v>88034</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594435</v>
+        <v>594412</v>
       </c>
       <c r="R13" t="n">
-        <v>6843227</v>
+        <v>6843245</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN13" t="n">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>1 substratenheter # förrötad klenare granlåga</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121455782</v>
+        <v>121455775</v>
       </c>
       <c r="B14" t="n">
-        <v>91153</v>
+        <v>90733</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2167,25 +2167,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594412</v>
+        <v>594314</v>
       </c>
       <c r="R14" t="n">
-        <v>6843245</v>
+        <v>6843411</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2239,12 +2239,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>bergskrön med gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AN14" t="n">
@@ -2252,7 +2253,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>1 substratenheter # 400-årig tall med stamsår</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2270,10 +2271,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121455775</v>
+        <v>121455781</v>
       </c>
       <c r="B15" t="n">
-        <v>90733</v>
+        <v>90999</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2286,21 +2287,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2310,10 +2311,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594314</v>
+        <v>594412</v>
       </c>
       <c r="R15" t="n">
-        <v>6843411</v>
+        <v>6843245</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2354,13 +2355,12 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>bergskrön med gammal hällmarkstallskog</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN15" t="n">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>1 substratenheter # 400-årig tall med stamsår</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2386,10 +2386,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121455774</v>
+        <v>121455777</v>
       </c>
       <c r="B16" t="n">
-        <v>79143</v>
+        <v>90999</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2402,21 +2402,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1352</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594327</v>
+        <v>594291</v>
       </c>
       <c r="R16" t="n">
-        <v>6843367</v>
+        <v>6843506</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2475,15 +2475,15 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>1 substratenheter # grenar på fallen äldre asp</t>
+          <t>2 substratenheter # förrötade grövre granlågor</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121455781</v>
+        <v>121455774</v>
       </c>
       <c r="B17" t="n">
-        <v>90999</v>
+        <v>79143</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2517,21 +2517,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1352</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594412</v>
+        <v>594327</v>
       </c>
       <c r="R17" t="n">
-        <v>6843245</v>
+        <v>6843367</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>1 substratenheter # grenar på fallen äldre asp</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121455777</v>
+        <v>121455779</v>
       </c>
       <c r="B18" t="n">
-        <v>90999</v>
+        <v>90713</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594291</v>
+        <v>594435</v>
       </c>
       <c r="R18" t="n">
-        <v>6843506</v>
+        <v>6843227</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2705,15 +2705,15 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+          <t>gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade grövre granlågor</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121455776</v>
+        <v>121455782</v>
       </c>
       <c r="B19" t="n">
-        <v>90713</v>
+        <v>91153</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2743,25 +2743,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594238</v>
+        <v>594412</v>
       </c>
       <c r="R19" t="n">
-        <v>6843576</v>
+        <v>6843245</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2820,15 +2820,15 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>relativt gammal grannaturskog i terrängsvacka</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade äldre granlågor</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121455778</v>
+        <v>121455776</v>
       </c>
       <c r="B20" t="n">
-        <v>90999</v>
+        <v>90713</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594430</v>
+        <v>594238</v>
       </c>
       <c r="R20" t="n">
-        <v>6843492</v>
+        <v>6843576</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2935,15 +2935,15 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+          <t>relativt gammal grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>2 substratenheter # förrötade äldre granlågor</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2959,6 +2959,1172 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121551293</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90714</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ofärnebrättingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>594547</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6843245</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121551304</v>
+      </c>
+      <c r="B22" t="n">
+        <v>74653</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ofärnebrättingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>594300</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6843515</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121551295</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91000</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>658</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ofärnebrättingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>594430</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6843483</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121551297</v>
+      </c>
+      <c r="B24" t="n">
+        <v>88035</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>510</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ofärnebrättingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>594431</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6843482</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121551276</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90714</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ofärnebrättingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>594521</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6843232</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121551329</v>
+      </c>
+      <c r="B26" t="n">
+        <v>88035</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>510</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ofärnebrättingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>594316</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6843272</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121551250</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90725</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ofärnebrättingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>594475</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6843224</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121551311</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80565</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ofärnebrättingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>594277</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6843575</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121551257</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91397</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ofärnebrättingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>594472</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6843244</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121551321</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91000</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>658</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ofärnebrättingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>594291</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6843558</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121551326</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90734</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ofärnebrättingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>594341</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6843401</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -1925,10 +1925,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121455778</v>
+        <v>121455777</v>
       </c>
       <c r="B12" t="n">
-        <v>90999</v>
+        <v>91005</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594430</v>
+        <v>594291</v>
       </c>
       <c r="R12" t="n">
-        <v>6843492</v>
+        <v>6843506</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2018,11 +2018,11 @@
         </is>
       </c>
       <c r="AN12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>2 substratenheter # förrötade grövre granlågor</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121455780</v>
+        <v>121455774</v>
       </c>
       <c r="B13" t="n">
-        <v>88034</v>
+        <v>79144</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>1352</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594412</v>
+        <v>594327</v>
       </c>
       <c r="R13" t="n">
-        <v>6843245</v>
+        <v>6843367</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
         </is>
       </c>
       <c r="AN13" t="n">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad klenare granlåga</t>
+          <t>1 substratenheter # grenar på fallen äldre asp</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121455775</v>
+        <v>121455778</v>
       </c>
       <c r="B14" t="n">
-        <v>90733</v>
+        <v>91005</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2171,21 +2171,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594314</v>
+        <v>594430</v>
       </c>
       <c r="R14" t="n">
-        <v>6843411</v>
+        <v>6843492</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2239,13 +2239,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>bergskrön med gammal hällmarkstallskog</t>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN14" t="n">
@@ -2253,7 +2252,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>1 substratenheter # 400-årig tall med stamsår</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2271,10 +2270,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121455781</v>
+        <v>121455775</v>
       </c>
       <c r="B15" t="n">
-        <v>90999</v>
+        <v>90739</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2287,21 +2286,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2311,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594412</v>
+        <v>594314</v>
       </c>
       <c r="R15" t="n">
-        <v>6843245</v>
+        <v>6843411</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2355,12 +2354,13 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>bergskrön med gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AN15" t="n">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>1 substratenheter # 400-årig tall med stamsår</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2386,10 +2386,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121455777</v>
+        <v>121455776</v>
       </c>
       <c r="B16" t="n">
-        <v>90999</v>
+        <v>90719</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2402,21 +2402,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594291</v>
+        <v>594238</v>
       </c>
       <c r="R16" t="n">
-        <v>6843506</v>
+        <v>6843576</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+          <t>relativt gammal grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN16" t="n">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade grövre granlågor</t>
+          <t>2 substratenheter # förrötade äldre granlågor</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121455774</v>
+        <v>121455779</v>
       </c>
       <c r="B17" t="n">
-        <v>79143</v>
+        <v>90719</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2517,21 +2517,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1352</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594327</v>
+        <v>594435</v>
       </c>
       <c r="R17" t="n">
-        <v>6843367</v>
+        <v>6843227</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
+          <t>gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>1 substratenheter # grenar på fallen äldre asp</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121455779</v>
+        <v>121455780</v>
       </c>
       <c r="B18" t="n">
-        <v>90713</v>
+        <v>88038</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594435</v>
+        <v>594412</v>
       </c>
       <c r="R18" t="n">
-        <v>6843227</v>
+        <v>6843245</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>1 substratenheter # förrötad klenare granlåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2734,7 +2734,7 @@
         <v>121455782</v>
       </c>
       <c r="B19" t="n">
-        <v>91153</v>
+        <v>91159</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121455776</v>
+        <v>121455781</v>
       </c>
       <c r="B20" t="n">
-        <v>90713</v>
+        <v>91005</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594238</v>
+        <v>594412</v>
       </c>
       <c r="R20" t="n">
-        <v>6843576</v>
+        <v>6843245</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2935,15 +2935,15 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>relativt gammal grannaturskog i terrängsvacka</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade äldre granlågor</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121551293</v>
+        <v>121551311</v>
       </c>
       <c r="B21" t="n">
-        <v>90714</v>
+        <v>80565</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594547</v>
+        <v>594277</v>
       </c>
       <c r="R21" t="n">
-        <v>6843245</v>
+        <v>6843575</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121551304</v>
+        <v>121551295</v>
       </c>
       <c r="B22" t="n">
-        <v>74653</v>
+        <v>91005</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3079,25 +3079,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594300</v>
+        <v>594430</v>
       </c>
       <c r="R22" t="n">
-        <v>6843515</v>
+        <v>6843483</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3173,10 +3173,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121551295</v>
+        <v>121551257</v>
       </c>
       <c r="B23" t="n">
-        <v>91000</v>
+        <v>91402</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3185,25 +3185,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594430</v>
+        <v>594472</v>
       </c>
       <c r="R23" t="n">
-        <v>6843483</v>
+        <v>6843244</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121551297</v>
+        <v>121551329</v>
       </c>
       <c r="B24" t="n">
-        <v>88035</v>
+        <v>88038</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594431</v>
+        <v>594316</v>
       </c>
       <c r="R24" t="n">
-        <v>6843482</v>
+        <v>6843272</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
         <v>121551276</v>
       </c>
       <c r="B25" t="n">
-        <v>90714</v>
+        <v>90719</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121551329</v>
+        <v>121551293</v>
       </c>
       <c r="B26" t="n">
-        <v>88035</v>
+        <v>90719</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3507,21 +3507,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594316</v>
+        <v>594547</v>
       </c>
       <c r="R26" t="n">
-        <v>6843272</v>
+        <v>6843245</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121551250</v>
+        <v>121551326</v>
       </c>
       <c r="B27" t="n">
-        <v>90725</v>
+        <v>90739</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3609,25 +3609,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1205</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594475</v>
+        <v>594341</v>
       </c>
       <c r="R27" t="n">
-        <v>6843224</v>
+        <v>6843401</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121551311</v>
+        <v>121551297</v>
       </c>
       <c r="B28" t="n">
-        <v>80565</v>
+        <v>88038</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3719,21 +3719,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594277</v>
+        <v>594431</v>
       </c>
       <c r="R28" t="n">
-        <v>6843575</v>
+        <v>6843482</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121551257</v>
+        <v>121551250</v>
       </c>
       <c r="B29" t="n">
-        <v>91397</v>
+        <v>90730</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3825,21 +3825,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>1205</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594472</v>
+        <v>594475</v>
       </c>
       <c r="R29" t="n">
-        <v>6843244</v>
+        <v>6843224</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3915,10 +3915,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121551321</v>
+        <v>121551304</v>
       </c>
       <c r="B30" t="n">
-        <v>91000</v>
+        <v>74653</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3927,25 +3927,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594291</v>
+        <v>594300</v>
       </c>
       <c r="R30" t="n">
-        <v>6843558</v>
+        <v>6843515</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121551326</v>
+        <v>121551321</v>
       </c>
       <c r="B31" t="n">
-        <v>90734</v>
+        <v>91005</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594341</v>
+        <v>594291</v>
       </c>
       <c r="R31" t="n">
-        <v>6843401</v>
+        <v>6843558</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>121455777</v>
       </c>
       <c r="B12" t="n">
-        <v>91005</v>
+        <v>91006</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121455774</v>
+        <v>121455780</v>
       </c>
       <c r="B13" t="n">
-        <v>79144</v>
+        <v>88039</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1352</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594327</v>
+        <v>594412</v>
       </c>
       <c r="R13" t="n">
-        <v>6843367</v>
+        <v>6843245</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN13" t="n">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 substratenheter # grenar på fallen äldre asp</t>
+          <t>1 substratenheter # förrötad klenare granlåga</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121455778</v>
+        <v>121455774</v>
       </c>
       <c r="B14" t="n">
-        <v>91005</v>
+        <v>79145</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2171,21 +2171,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1352</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594430</v>
+        <v>594327</v>
       </c>
       <c r="R14" t="n">
-        <v>6843492</v>
+        <v>6843367</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
         </is>
       </c>
       <c r="AN14" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>1 substratenheter # grenar på fallen äldre asp</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121455775</v>
+        <v>121455781</v>
       </c>
       <c r="B15" t="n">
-        <v>90739</v>
+        <v>91006</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594314</v>
+        <v>594412</v>
       </c>
       <c r="R15" t="n">
-        <v>6843411</v>
+        <v>6843245</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2354,13 +2354,12 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>bergskrön med gammal hällmarkstallskog</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN15" t="n">
@@ -2368,7 +2367,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>1 substratenheter # 400-årig tall med stamsår</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2389,7 +2388,7 @@
         <v>121455776</v>
       </c>
       <c r="B16" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2501,10 +2500,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121455779</v>
+        <v>121455782</v>
       </c>
       <c r="B17" t="n">
-        <v>90719</v>
+        <v>91160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2513,25 +2512,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2541,10 +2540,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594435</v>
+        <v>594412</v>
       </c>
       <c r="R17" t="n">
-        <v>6843227</v>
+        <v>6843245</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2590,7 +2589,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -2616,10 +2615,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121455780</v>
+        <v>121455779</v>
       </c>
       <c r="B18" t="n">
-        <v>88038</v>
+        <v>90720</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,21 +2631,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2656,10 +2655,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594412</v>
+        <v>594435</v>
       </c>
       <c r="R18" t="n">
-        <v>6843245</v>
+        <v>6843227</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2705,7 +2704,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -2713,7 +2712,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad klenare granlåga</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2731,10 +2730,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121455782</v>
+        <v>121455778</v>
       </c>
       <c r="B19" t="n">
-        <v>91159</v>
+        <v>91006</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2743,25 +2742,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2771,10 +2770,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594412</v>
+        <v>594430</v>
       </c>
       <c r="R19" t="n">
-        <v>6843245</v>
+        <v>6843492</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2820,7 +2819,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -2846,10 +2845,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121455781</v>
+        <v>121455775</v>
       </c>
       <c r="B20" t="n">
-        <v>91005</v>
+        <v>90740</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2862,21 +2861,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2886,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594412</v>
+        <v>594314</v>
       </c>
       <c r="R20" t="n">
-        <v>6843245</v>
+        <v>6843411</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2930,12 +2929,13 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>bergskrön med gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>1 substratenheter # 400-årig tall med stamsår</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121551311</v>
+        <v>121551295</v>
       </c>
       <c r="B21" t="n">
-        <v>80565</v>
+        <v>91006</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594277</v>
+        <v>594430</v>
       </c>
       <c r="R21" t="n">
-        <v>6843575</v>
+        <v>6843483</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121551295</v>
+        <v>121551297</v>
       </c>
       <c r="B22" t="n">
-        <v>91005</v>
+        <v>88039</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3083,21 +3083,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594430</v>
+        <v>594431</v>
       </c>
       <c r="R22" t="n">
-        <v>6843483</v>
+        <v>6843482</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3173,10 +3173,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121551257</v>
+        <v>121551311</v>
       </c>
       <c r="B23" t="n">
-        <v>91402</v>
+        <v>80566</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3185,25 +3185,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594472</v>
+        <v>594277</v>
       </c>
       <c r="R23" t="n">
-        <v>6843244</v>
+        <v>6843575</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121551329</v>
+        <v>121551321</v>
       </c>
       <c r="B24" t="n">
-        <v>88038</v>
+        <v>91006</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594316</v>
+        <v>594291</v>
       </c>
       <c r="R24" t="n">
-        <v>6843272</v>
+        <v>6843558</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121551276</v>
+        <v>121551329</v>
       </c>
       <c r="B25" t="n">
-        <v>90719</v>
+        <v>88039</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3401,21 +3401,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594521</v>
+        <v>594316</v>
       </c>
       <c r="R25" t="n">
-        <v>6843232</v>
+        <v>6843272</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,10 +3491,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121551293</v>
+        <v>121551326</v>
       </c>
       <c r="B26" t="n">
-        <v>90719</v>
+        <v>90740</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3507,21 +3507,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594547</v>
+        <v>594341</v>
       </c>
       <c r="R26" t="n">
-        <v>6843245</v>
+        <v>6843401</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121551326</v>
+        <v>121551257</v>
       </c>
       <c r="B27" t="n">
-        <v>90739</v>
+        <v>91403</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3609,25 +3609,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594341</v>
+        <v>594472</v>
       </c>
       <c r="R27" t="n">
-        <v>6843401</v>
+        <v>6843244</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121551297</v>
+        <v>121551250</v>
       </c>
       <c r="B28" t="n">
-        <v>88038</v>
+        <v>90731</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3715,25 +3715,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>1205</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594431</v>
+        <v>594475</v>
       </c>
       <c r="R28" t="n">
-        <v>6843482</v>
+        <v>6843224</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121551250</v>
+        <v>121551304</v>
       </c>
       <c r="B29" t="n">
-        <v>90730</v>
+        <v>74654</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3825,21 +3825,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1205</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594475</v>
+        <v>594300</v>
       </c>
       <c r="R29" t="n">
-        <v>6843224</v>
+        <v>6843515</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3915,10 +3915,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121551304</v>
+        <v>121551276</v>
       </c>
       <c r="B30" t="n">
-        <v>74653</v>
+        <v>90720</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3927,25 +3927,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594300</v>
+        <v>594521</v>
       </c>
       <c r="R30" t="n">
-        <v>6843515</v>
+        <v>6843232</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121551321</v>
+        <v>121551293</v>
       </c>
       <c r="B31" t="n">
-        <v>91005</v>
+        <v>90720</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594291</v>
+        <v>594547</v>
       </c>
       <c r="R31" t="n">
-        <v>6843558</v>
+        <v>6843245</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -1925,7 +1925,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121455777</v>
+        <v>121455781</v>
       </c>
       <c r="B12" t="n">
         <v>91006</v>
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594291</v>
+        <v>594412</v>
       </c>
       <c r="R12" t="n">
-        <v>6843506</v>
+        <v>6843245</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2014,15 +2014,15 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade grövre granlågor</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121455780</v>
+        <v>121455777</v>
       </c>
       <c r="B13" t="n">
-        <v>88039</v>
+        <v>91006</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594412</v>
+        <v>594291</v>
       </c>
       <c r="R13" t="n">
-        <v>6843245</v>
+        <v>6843506</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2129,15 +2129,15 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad klenare granlåga</t>
+          <t>2 substratenheter # förrötade grövre granlågor</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121455774</v>
+        <v>121455779</v>
       </c>
       <c r="B14" t="n">
-        <v>79145</v>
+        <v>90720</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2171,21 +2171,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1352</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594327</v>
+        <v>594435</v>
       </c>
       <c r="R14" t="n">
-        <v>6843367</v>
+        <v>6843227</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
+          <t>gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN14" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>1 substratenheter # grenar på fallen äldre asp</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121455781</v>
+        <v>121455776</v>
       </c>
       <c r="B15" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594412</v>
+        <v>594238</v>
       </c>
       <c r="R15" t="n">
-        <v>6843245</v>
+        <v>6843576</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2359,15 +2359,15 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>2 substratenheter # förrötade äldre granlågor</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121455776</v>
+        <v>121455774</v>
       </c>
       <c r="B16" t="n">
-        <v>90720</v>
+        <v>79145</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2401,21 +2401,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1352</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594238</v>
+        <v>594327</v>
       </c>
       <c r="R16" t="n">
-        <v>6843576</v>
+        <v>6843367</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2474,15 +2474,15 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>relativt gammal grannaturskog i terrängsvacka</t>
+          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
         </is>
       </c>
       <c r="AN16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade äldre granlågor</t>
+          <t>1 substratenheter # grenar på fallen äldre asp</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121455779</v>
+        <v>121455780</v>
       </c>
       <c r="B18" t="n">
-        <v>90720</v>
+        <v>88039</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594435</v>
+        <v>594412</v>
       </c>
       <c r="R18" t="n">
-        <v>6843227</v>
+        <v>6843245</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>1 substratenheter # förrötad klenare granlåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121551295</v>
+        <v>121551293</v>
       </c>
       <c r="B21" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594430</v>
+        <v>594547</v>
       </c>
       <c r="R21" t="n">
-        <v>6843483</v>
+        <v>6843245</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121551297</v>
+        <v>121551326</v>
       </c>
       <c r="B22" t="n">
-        <v>88039</v>
+        <v>90740</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3083,21 +3083,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594431</v>
+        <v>594341</v>
       </c>
       <c r="R22" t="n">
-        <v>6843482</v>
+        <v>6843401</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3173,10 +3173,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121551311</v>
+        <v>121551329</v>
       </c>
       <c r="B23" t="n">
-        <v>80566</v>
+        <v>88039</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3189,21 +3189,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594277</v>
+        <v>594316</v>
       </c>
       <c r="R23" t="n">
-        <v>6843575</v>
+        <v>6843272</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121551321</v>
+        <v>121551257</v>
       </c>
       <c r="B24" t="n">
-        <v>91006</v>
+        <v>91403</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3291,25 +3291,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594291</v>
+        <v>594472</v>
       </c>
       <c r="R24" t="n">
-        <v>6843558</v>
+        <v>6843244</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121551329</v>
+        <v>121551295</v>
       </c>
       <c r="B25" t="n">
-        <v>88039</v>
+        <v>91006</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3401,21 +3401,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594316</v>
+        <v>594430</v>
       </c>
       <c r="R25" t="n">
-        <v>6843272</v>
+        <v>6843483</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,10 +3491,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121551326</v>
+        <v>121551311</v>
       </c>
       <c r="B26" t="n">
-        <v>90740</v>
+        <v>80566</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3507,21 +3507,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594341</v>
+        <v>594277</v>
       </c>
       <c r="R26" t="n">
-        <v>6843401</v>
+        <v>6843575</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121551257</v>
+        <v>121551304</v>
       </c>
       <c r="B27" t="n">
-        <v>91403</v>
+        <v>74654</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594472</v>
+        <v>594300</v>
       </c>
       <c r="R27" t="n">
-        <v>6843244</v>
+        <v>6843515</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121551250</v>
+        <v>121551297</v>
       </c>
       <c r="B28" t="n">
-        <v>90731</v>
+        <v>88039</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3715,25 +3715,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1205</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594475</v>
+        <v>594431</v>
       </c>
       <c r="R28" t="n">
-        <v>6843224</v>
+        <v>6843482</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121551304</v>
+        <v>121551321</v>
       </c>
       <c r="B29" t="n">
-        <v>74654</v>
+        <v>91006</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3821,25 +3821,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594300</v>
+        <v>594291</v>
       </c>
       <c r="R29" t="n">
-        <v>6843515</v>
+        <v>6843558</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121551293</v>
+        <v>121551250</v>
       </c>
       <c r="B31" t="n">
-        <v>90720</v>
+        <v>90731</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4033,25 +4033,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594547</v>
+        <v>594475</v>
       </c>
       <c r="R31" t="n">
-        <v>6843245</v>
+        <v>6843224</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -1925,7 +1925,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121455781</v>
+        <v>121455777</v>
       </c>
       <c r="B12" t="n">
         <v>91006</v>
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594412</v>
+        <v>594291</v>
       </c>
       <c r="R12" t="n">
-        <v>6843245</v>
+        <v>6843506</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2014,15 +2014,15 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>2 substratenheter # förrötade grövre granlågor</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121455777</v>
+        <v>121455780</v>
       </c>
       <c r="B13" t="n">
-        <v>91006</v>
+        <v>88039</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594291</v>
+        <v>594412</v>
       </c>
       <c r="R13" t="n">
-        <v>6843506</v>
+        <v>6843245</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2129,15 +2129,15 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade grövre granlågor</t>
+          <t>1 substratenheter # förrötad klenare granlåga</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121455779</v>
+        <v>121455778</v>
       </c>
       <c r="B14" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2171,21 +2171,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594435</v>
+        <v>594430</v>
       </c>
       <c r="R14" t="n">
-        <v>6843227</v>
+        <v>6843492</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN14" t="n">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121455776</v>
+        <v>121455775</v>
       </c>
       <c r="B15" t="n">
-        <v>90720</v>
+        <v>90740</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594238</v>
+        <v>594314</v>
       </c>
       <c r="R15" t="n">
-        <v>6843576</v>
+        <v>6843411</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2354,20 +2354,21 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>relativt gammal grannaturskog i terrängsvacka</t>
+          <t>bergskrön med gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AN15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade äldre granlågor</t>
+          <t>1 substratenheter # 400-årig tall med stamsår</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2385,10 +2386,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121455774</v>
+        <v>121455781</v>
       </c>
       <c r="B16" t="n">
-        <v>79145</v>
+        <v>91006</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2401,21 +2402,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1352</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2425,10 +2426,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594327</v>
+        <v>594412</v>
       </c>
       <c r="R16" t="n">
-        <v>6843367</v>
+        <v>6843245</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2474,7 +2475,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN16" t="n">
@@ -2482,7 +2483,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>1 substratenheter # grenar på fallen äldre asp</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2500,10 +2501,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121455782</v>
+        <v>121455776</v>
       </c>
       <c r="B17" t="n">
-        <v>91160</v>
+        <v>90720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2512,25 +2513,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2540,10 +2541,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594412</v>
+        <v>594238</v>
       </c>
       <c r="R17" t="n">
-        <v>6843245</v>
+        <v>6843576</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2589,15 +2590,15 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>2 substratenheter # förrötade äldre granlågor</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2615,10 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121455780</v>
+        <v>121455782</v>
       </c>
       <c r="B18" t="n">
-        <v>88039</v>
+        <v>91160</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2627,25 +2628,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2712,7 +2713,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad klenare granlåga</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2730,10 +2731,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121455778</v>
+        <v>121455774</v>
       </c>
       <c r="B19" t="n">
-        <v>91006</v>
+        <v>79145</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2746,21 +2747,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1352</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2770,10 +2771,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594430</v>
+        <v>594327</v>
       </c>
       <c r="R19" t="n">
-        <v>6843492</v>
+        <v>6843367</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2819,7 +2820,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -2827,7 +2828,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>1 substratenheter # grenar på fallen äldre asp</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2845,10 +2846,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121455775</v>
+        <v>121455779</v>
       </c>
       <c r="B20" t="n">
-        <v>90740</v>
+        <v>90720</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2861,21 +2862,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2886,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594314</v>
+        <v>594435</v>
       </c>
       <c r="R20" t="n">
-        <v>6843411</v>
+        <v>6843227</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2929,13 +2930,12 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>bergskrön med gammal hällmarkstallskog</t>
+          <t>gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>1 substratenheter # 400-årig tall med stamsår</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121551293</v>
+        <v>121551321</v>
       </c>
       <c r="B21" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594547</v>
+        <v>594291</v>
       </c>
       <c r="R21" t="n">
-        <v>6843245</v>
+        <v>6843558</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121551326</v>
+        <v>121551297</v>
       </c>
       <c r="B22" t="n">
-        <v>90740</v>
+        <v>88039</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3083,21 +3083,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594341</v>
+        <v>594431</v>
       </c>
       <c r="R22" t="n">
-        <v>6843401</v>
+        <v>6843482</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3173,10 +3173,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121551329</v>
+        <v>121551250</v>
       </c>
       <c r="B23" t="n">
-        <v>88039</v>
+        <v>90731</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3185,25 +3185,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>1205</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594316</v>
+        <v>594475</v>
       </c>
       <c r="R23" t="n">
-        <v>6843272</v>
+        <v>6843224</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121551257</v>
+        <v>121551276</v>
       </c>
       <c r="B24" t="n">
-        <v>91403</v>
+        <v>90720</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3291,25 +3291,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594472</v>
+        <v>594521</v>
       </c>
       <c r="R24" t="n">
-        <v>6843244</v>
+        <v>6843232</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3703,7 +3703,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121551297</v>
+        <v>121551329</v>
       </c>
       <c r="B28" t="n">
         <v>88039</v>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594431</v>
+        <v>594316</v>
       </c>
       <c r="R28" t="n">
-        <v>6843482</v>
+        <v>6843272</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121551321</v>
+        <v>121551293</v>
       </c>
       <c r="B29" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3825,21 +3825,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594291</v>
+        <v>594547</v>
       </c>
       <c r="R29" t="n">
-        <v>6843558</v>
+        <v>6843245</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3915,10 +3915,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121551276</v>
+        <v>121551257</v>
       </c>
       <c r="B30" t="n">
-        <v>90720</v>
+        <v>91403</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3927,25 +3927,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594521</v>
+        <v>594472</v>
       </c>
       <c r="R30" t="n">
-        <v>6843232</v>
+        <v>6843244</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121551250</v>
+        <v>121551326</v>
       </c>
       <c r="B31" t="n">
-        <v>90731</v>
+        <v>90740</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4033,25 +4033,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1205</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594475</v>
+        <v>594341</v>
       </c>
       <c r="R31" t="n">
-        <v>6843224</v>
+        <v>6843401</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -1925,7 +1925,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121455777</v>
+        <v>121455781</v>
       </c>
       <c r="B12" t="n">
         <v>91006</v>
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594291</v>
+        <v>594412</v>
       </c>
       <c r="R12" t="n">
-        <v>6843506</v>
+        <v>6843245</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2014,15 +2014,15 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade grövre granlågor</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121455780</v>
+        <v>121455776</v>
       </c>
       <c r="B13" t="n">
-        <v>88039</v>
+        <v>90720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594412</v>
+        <v>594238</v>
       </c>
       <c r="R13" t="n">
-        <v>6843245</v>
+        <v>6843576</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2129,15 +2129,15 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad klenare granlåga</t>
+          <t>2 substratenheter # förrötade äldre granlågor</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121455778</v>
+        <v>121455774</v>
       </c>
       <c r="B14" t="n">
-        <v>91006</v>
+        <v>79145</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2171,21 +2171,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1352</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594430</v>
+        <v>594327</v>
       </c>
       <c r="R14" t="n">
-        <v>6843492</v>
+        <v>6843367</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
         </is>
       </c>
       <c r="AN14" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>1 substratenheter # grenar på fallen äldre asp</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2386,10 +2386,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121455781</v>
+        <v>121455779</v>
       </c>
       <c r="B16" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2402,21 +2402,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594412</v>
+        <v>594435</v>
       </c>
       <c r="R16" t="n">
-        <v>6843245</v>
+        <v>6843227</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN16" t="n">
@@ -2501,10 +2501,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121455776</v>
+        <v>121455777</v>
       </c>
       <c r="B17" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2517,21 +2517,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594238</v>
+        <v>594291</v>
       </c>
       <c r="R17" t="n">
-        <v>6843576</v>
+        <v>6843506</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>relativt gammal grannaturskog i terrängsvacka</t>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade äldre granlågor</t>
+          <t>2 substratenheter # förrötade grövre granlågor</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121455782</v>
+        <v>121455778</v>
       </c>
       <c r="B18" t="n">
-        <v>91160</v>
+        <v>91006</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2628,25 +2628,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594412</v>
+        <v>594430</v>
       </c>
       <c r="R18" t="n">
-        <v>6843245</v>
+        <v>6843492</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -2731,10 +2731,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121455774</v>
+        <v>121455782</v>
       </c>
       <c r="B19" t="n">
-        <v>79145</v>
+        <v>91160</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2743,25 +2743,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1352</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594327</v>
+        <v>594412</v>
       </c>
       <c r="R19" t="n">
-        <v>6843367</v>
+        <v>6843245</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>1 substratenheter # grenar på fallen äldre asp</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121455779</v>
+        <v>121455780</v>
       </c>
       <c r="B20" t="n">
-        <v>90720</v>
+        <v>88039</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594435</v>
+        <v>594412</v>
       </c>
       <c r="R20" t="n">
-        <v>6843227</v>
+        <v>6843245</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>1 substratenheter # förrötad klenare granlåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121551321</v>
+        <v>121551293</v>
       </c>
       <c r="B21" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594291</v>
+        <v>594547</v>
       </c>
       <c r="R21" t="n">
-        <v>6843558</v>
+        <v>6843245</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121551297</v>
+        <v>121551304</v>
       </c>
       <c r="B22" t="n">
-        <v>88039</v>
+        <v>74654</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3079,25 +3079,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594431</v>
+        <v>594300</v>
       </c>
       <c r="R22" t="n">
-        <v>6843482</v>
+        <v>6843515</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3173,10 +3173,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121551250</v>
+        <v>121551295</v>
       </c>
       <c r="B23" t="n">
-        <v>90731</v>
+        <v>91006</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3185,25 +3185,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1205</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594475</v>
+        <v>594430</v>
       </c>
       <c r="R23" t="n">
-        <v>6843224</v>
+        <v>6843483</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121551276</v>
+        <v>121551321</v>
       </c>
       <c r="B24" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594521</v>
+        <v>594291</v>
       </c>
       <c r="R24" t="n">
-        <v>6843232</v>
+        <v>6843558</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121551295</v>
+        <v>121551326</v>
       </c>
       <c r="B25" t="n">
-        <v>91006</v>
+        <v>90740</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3401,21 +3401,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594430</v>
+        <v>594341</v>
       </c>
       <c r="R25" t="n">
-        <v>6843483</v>
+        <v>6843401</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,10 +3491,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121551311</v>
+        <v>121551257</v>
       </c>
       <c r="B26" t="n">
-        <v>80566</v>
+        <v>91403</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3503,25 +3503,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594277</v>
+        <v>594472</v>
       </c>
       <c r="R26" t="n">
-        <v>6843575</v>
+        <v>6843244</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121551304</v>
+        <v>121551297</v>
       </c>
       <c r="B27" t="n">
-        <v>74654</v>
+        <v>88039</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3609,25 +3609,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>510</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594300</v>
+        <v>594431</v>
       </c>
       <c r="R27" t="n">
-        <v>6843515</v>
+        <v>6843482</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121551329</v>
+        <v>121551250</v>
       </c>
       <c r="B28" t="n">
-        <v>88039</v>
+        <v>90731</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3715,25 +3715,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>1205</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594316</v>
+        <v>594475</v>
       </c>
       <c r="R28" t="n">
-        <v>6843272</v>
+        <v>6843224</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121551293</v>
+        <v>121551311</v>
       </c>
       <c r="B29" t="n">
-        <v>90720</v>
+        <v>80566</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3825,21 +3825,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594547</v>
+        <v>594277</v>
       </c>
       <c r="R29" t="n">
-        <v>6843245</v>
+        <v>6843575</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3915,10 +3915,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121551257</v>
+        <v>121551276</v>
       </c>
       <c r="B30" t="n">
-        <v>91403</v>
+        <v>90720</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3927,25 +3927,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594472</v>
+        <v>594521</v>
       </c>
       <c r="R30" t="n">
-        <v>6843244</v>
+        <v>6843232</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121551326</v>
+        <v>121551329</v>
       </c>
       <c r="B31" t="n">
-        <v>90740</v>
+        <v>88039</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594341</v>
+        <v>594316</v>
       </c>
       <c r="R31" t="n">
-        <v>6843401</v>
+        <v>6843272</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -1925,7 +1925,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121455778</v>
+        <v>121455777</v>
       </c>
       <c r="B12" t="n">
         <v>91014</v>
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594430</v>
+        <v>594291</v>
       </c>
       <c r="R12" t="n">
-        <v>6843492</v>
+        <v>6843506</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2018,11 +2018,11 @@
         </is>
       </c>
       <c r="AN12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>2 substratenheter # förrötade grövre granlågor</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121455774</v>
+        <v>121455782</v>
       </c>
       <c r="B13" t="n">
-        <v>79152</v>
+        <v>91168</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2052,25 +2052,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1352</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594327</v>
+        <v>594412</v>
       </c>
       <c r="R13" t="n">
-        <v>6843367</v>
+        <v>6843245</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN13" t="n">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 substratenheter # grenar på fallen äldre asp</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121455775</v>
+        <v>121455780</v>
       </c>
       <c r="B14" t="n">
-        <v>90748</v>
+        <v>88046</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2171,21 +2171,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594314</v>
+        <v>594412</v>
       </c>
       <c r="R14" t="n">
-        <v>6843411</v>
+        <v>6843245</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2239,13 +2239,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>bergskrön med gammal hällmarkstallskog</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN14" t="n">
@@ -2253,7 +2252,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>1 substratenheter # 400-årig tall med stamsår</t>
+          <t>1 substratenheter # förrötad klenare granlåga</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2271,10 +2270,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121455781</v>
+        <v>121455779</v>
       </c>
       <c r="B15" t="n">
-        <v>91014</v>
+        <v>90728</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2287,21 +2286,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2311,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594412</v>
+        <v>594435</v>
       </c>
       <c r="R15" t="n">
-        <v>6843245</v>
+        <v>6843227</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2360,7 +2359,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN15" t="n">
@@ -2386,10 +2385,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121455776</v>
+        <v>121455775</v>
       </c>
       <c r="B16" t="n">
-        <v>90728</v>
+        <v>90748</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2402,21 +2401,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2426,10 +2425,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594238</v>
+        <v>594314</v>
       </c>
       <c r="R16" t="n">
-        <v>6843576</v>
+        <v>6843411</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2470,20 +2469,21 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>relativt gammal grannaturskog i terrängsvacka</t>
+          <t>bergskrön med gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AN16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade äldre granlågor</t>
+          <t>1 substratenheter # 400-årig tall med stamsår</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121455782</v>
+        <v>121455778</v>
       </c>
       <c r="B17" t="n">
-        <v>91168</v>
+        <v>91014</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2513,25 +2513,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594412</v>
+        <v>594430</v>
       </c>
       <c r="R17" t="n">
-        <v>6843245</v>
+        <v>6843492</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -2616,10 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121455779</v>
+        <v>121455781</v>
       </c>
       <c r="B18" t="n">
-        <v>90728</v>
+        <v>91014</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594435</v>
+        <v>594412</v>
       </c>
       <c r="R18" t="n">
-        <v>6843227</v>
+        <v>6843245</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -2731,10 +2731,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121455777</v>
+        <v>121455774</v>
       </c>
       <c r="B19" t="n">
-        <v>91014</v>
+        <v>79152</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1352</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594291</v>
+        <v>594327</v>
       </c>
       <c r="R19" t="n">
-        <v>6843506</v>
+        <v>6843367</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2820,15 +2820,15 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
         </is>
       </c>
       <c r="AN19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade grövre granlågor</t>
+          <t>1 substratenheter # grenar på fallen äldre asp</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121455780</v>
+        <v>121455776</v>
       </c>
       <c r="B20" t="n">
-        <v>88046</v>
+        <v>90728</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594412</v>
+        <v>594238</v>
       </c>
       <c r="R20" t="n">
-        <v>6843245</v>
+        <v>6843576</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2935,15 +2935,15 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad klenare granlåga</t>
+          <t>2 substratenheter # förrötade äldre granlågor</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121551329</v>
+        <v>121551321</v>
       </c>
       <c r="B21" t="n">
-        <v>88046</v>
+        <v>91014</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594316</v>
+        <v>594291</v>
       </c>
       <c r="R21" t="n">
-        <v>6843272</v>
+        <v>6843558</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121551276</v>
+        <v>121551304</v>
       </c>
       <c r="B22" t="n">
-        <v>90728</v>
+        <v>74661</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3079,25 +3079,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594521</v>
+        <v>594300</v>
       </c>
       <c r="R22" t="n">
-        <v>6843232</v>
+        <v>6843515</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3166,17 +3166,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121551295</v>
+        <v>121551297</v>
       </c>
       <c r="B23" t="n">
-        <v>91014</v>
+        <v>88046</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3189,21 +3189,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594430</v>
+        <v>594431</v>
       </c>
       <c r="R23" t="n">
-        <v>6843483</v>
+        <v>6843482</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121551311</v>
+        <v>121551257</v>
       </c>
       <c r="B24" t="n">
-        <v>80573</v>
+        <v>91411</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3291,25 +3291,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1049</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594277</v>
+        <v>594472</v>
       </c>
       <c r="R24" t="n">
-        <v>6843575</v>
+        <v>6843244</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3491,10 +3491,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121551326</v>
+        <v>121551295</v>
       </c>
       <c r="B26" t="n">
-        <v>90748</v>
+        <v>91014</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3507,21 +3507,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594341</v>
+        <v>594430</v>
       </c>
       <c r="R26" t="n">
-        <v>6843401</v>
+        <v>6843483</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121551257</v>
+        <v>121551311</v>
       </c>
       <c r="B27" t="n">
-        <v>91411</v>
+        <v>80573</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3609,25 +3609,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594472</v>
+        <v>594277</v>
       </c>
       <c r="R27" t="n">
-        <v>6843244</v>
+        <v>6843575</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3696,17 +3696,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121551321</v>
+        <v>121551326</v>
       </c>
       <c r="B28" t="n">
-        <v>91014</v>
+        <v>90748</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3719,21 +3719,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594291</v>
+        <v>594341</v>
       </c>
       <c r="R28" t="n">
-        <v>6843558</v>
+        <v>6843401</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121551297</v>
+        <v>121551250</v>
       </c>
       <c r="B29" t="n">
-        <v>88046</v>
+        <v>90739</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3821,25 +3821,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>1205</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594431</v>
+        <v>594475</v>
       </c>
       <c r="R29" t="n">
-        <v>6843482</v>
+        <v>6843224</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3915,10 +3915,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121551250</v>
+        <v>121551329</v>
       </c>
       <c r="B30" t="n">
-        <v>90739</v>
+        <v>88046</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3927,25 +3927,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1205</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594475</v>
+        <v>594316</v>
       </c>
       <c r="R30" t="n">
-        <v>6843224</v>
+        <v>6843272</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4014,17 +4014,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121551304</v>
+        <v>121551276</v>
       </c>
       <c r="B31" t="n">
-        <v>74661</v>
+        <v>90728</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4033,25 +4033,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594300</v>
+        <v>594521</v>
       </c>
       <c r="R31" t="n">
-        <v>6843515</v>
+        <v>6843232</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -3173,10 +3173,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121551297</v>
+        <v>121551257</v>
       </c>
       <c r="B23" t="n">
-        <v>88046</v>
+        <v>91411</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3185,25 +3185,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594431</v>
+        <v>594472</v>
       </c>
       <c r="R23" t="n">
-        <v>6843482</v>
+        <v>6843244</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121551257</v>
+        <v>121551297</v>
       </c>
       <c r="B24" t="n">
-        <v>91411</v>
+        <v>88046</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3291,25 +3291,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594472</v>
+        <v>594431</v>
       </c>
       <c r="R24" t="n">
-        <v>6843244</v>
+        <v>6843482</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121551311</v>
+        <v>121551326</v>
       </c>
       <c r="B27" t="n">
-        <v>80573</v>
+        <v>90748</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594277</v>
+        <v>594341</v>
       </c>
       <c r="R27" t="n">
-        <v>6843575</v>
+        <v>6843401</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121551326</v>
+        <v>121551311</v>
       </c>
       <c r="B28" t="n">
-        <v>90748</v>
+        <v>80573</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3719,21 +3719,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594341</v>
+        <v>594277</v>
       </c>
       <c r="R28" t="n">
-        <v>6843401</v>
+        <v>6843575</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -3067,10 +3067,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121551304</v>
+        <v>121551329</v>
       </c>
       <c r="B22" t="n">
-        <v>74661</v>
+        <v>88046</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3079,25 +3079,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594300</v>
+        <v>594316</v>
       </c>
       <c r="R22" t="n">
-        <v>6843515</v>
+        <v>6843272</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3173,10 +3173,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121551257</v>
+        <v>121551293</v>
       </c>
       <c r="B23" t="n">
-        <v>91411</v>
+        <v>90728</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3185,25 +3185,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594472</v>
+        <v>594547</v>
       </c>
       <c r="R23" t="n">
-        <v>6843244</v>
+        <v>6843245</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121551297</v>
+        <v>121551295</v>
       </c>
       <c r="B24" t="n">
-        <v>88046</v>
+        <v>91014</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594431</v>
+        <v>594430</v>
       </c>
       <c r="R24" t="n">
-        <v>6843482</v>
+        <v>6843483</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3385,7 +3385,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121551293</v>
+        <v>121551276</v>
       </c>
       <c r="B25" t="n">
         <v>90728</v>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594547</v>
+        <v>594521</v>
       </c>
       <c r="R25" t="n">
-        <v>6843245</v>
+        <v>6843232</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,10 +3491,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121551295</v>
+        <v>121551326</v>
       </c>
       <c r="B26" t="n">
-        <v>91014</v>
+        <v>90748</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3507,21 +3507,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594430</v>
+        <v>594341</v>
       </c>
       <c r="R26" t="n">
-        <v>6843483</v>
+        <v>6843401</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121551326</v>
+        <v>121551304</v>
       </c>
       <c r="B27" t="n">
-        <v>90748</v>
+        <v>74661</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3609,25 +3609,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594341</v>
+        <v>594300</v>
       </c>
       <c r="R27" t="n">
-        <v>6843401</v>
+        <v>6843515</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121551311</v>
+        <v>121551297</v>
       </c>
       <c r="B28" t="n">
-        <v>80573</v>
+        <v>88046</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3719,21 +3719,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594277</v>
+        <v>594431</v>
       </c>
       <c r="R28" t="n">
-        <v>6843575</v>
+        <v>6843482</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3915,10 +3915,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121551329</v>
+        <v>121551311</v>
       </c>
       <c r="B30" t="n">
-        <v>88046</v>
+        <v>80573</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3931,21 +3931,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>1049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594316</v>
+        <v>594277</v>
       </c>
       <c r="R30" t="n">
-        <v>6843272</v>
+        <v>6843575</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121551276</v>
+        <v>121551257</v>
       </c>
       <c r="B31" t="n">
-        <v>90728</v>
+        <v>91411</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4033,25 +4033,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594521</v>
+        <v>594472</v>
       </c>
       <c r="R31" t="n">
-        <v>6843232</v>
+        <v>6843244</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -3067,10 +3067,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121551329</v>
+        <v>121551293</v>
       </c>
       <c r="B22" t="n">
-        <v>88046</v>
+        <v>90728</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3083,21 +3083,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594316</v>
+        <v>594547</v>
       </c>
       <c r="R22" t="n">
-        <v>6843272</v>
+        <v>6843245</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3173,10 +3173,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121551293</v>
+        <v>121551329</v>
       </c>
       <c r="B23" t="n">
-        <v>90728</v>
+        <v>88046</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3189,21 +3189,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594547</v>
+        <v>594316</v>
       </c>
       <c r="R23" t="n">
-        <v>6843245</v>
+        <v>6843272</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -2961,10 +2961,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121551321</v>
+        <v>121551304</v>
       </c>
       <c r="B21" t="n">
-        <v>91014</v>
+        <v>74661</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2973,25 +2973,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594291</v>
+        <v>594300</v>
       </c>
       <c r="R21" t="n">
-        <v>6843558</v>
+        <v>6843515</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3067,7 +3067,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121551293</v>
+        <v>121551276</v>
       </c>
       <c r="B22" t="n">
         <v>90728</v>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594547</v>
+        <v>594521</v>
       </c>
       <c r="R22" t="n">
-        <v>6843245</v>
+        <v>6843232</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3173,10 +3173,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121551329</v>
+        <v>121551295</v>
       </c>
       <c r="B23" t="n">
-        <v>88046</v>
+        <v>91014</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3189,21 +3189,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594316</v>
+        <v>594430</v>
       </c>
       <c r="R23" t="n">
-        <v>6843272</v>
+        <v>6843483</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121551295</v>
+        <v>121551326</v>
       </c>
       <c r="B24" t="n">
-        <v>91014</v>
+        <v>90748</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594430</v>
+        <v>594341</v>
       </c>
       <c r="R24" t="n">
-        <v>6843483</v>
+        <v>6843401</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121551276</v>
+        <v>121551329</v>
       </c>
       <c r="B25" t="n">
-        <v>90728</v>
+        <v>88046</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3401,21 +3401,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594521</v>
+        <v>594316</v>
       </c>
       <c r="R25" t="n">
-        <v>6843232</v>
+        <v>6843272</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,10 +3491,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121551326</v>
+        <v>121551321</v>
       </c>
       <c r="B26" t="n">
-        <v>90748</v>
+        <v>91014</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3507,21 +3507,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594341</v>
+        <v>594291</v>
       </c>
       <c r="R26" t="n">
-        <v>6843401</v>
+        <v>6843558</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121551304</v>
+        <v>121551250</v>
       </c>
       <c r="B27" t="n">
-        <v>74661</v>
+        <v>90739</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>1205</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594300</v>
+        <v>594475</v>
       </c>
       <c r="R27" t="n">
-        <v>6843515</v>
+        <v>6843224</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121551250</v>
+        <v>121551293</v>
       </c>
       <c r="B29" t="n">
-        <v>90739</v>
+        <v>90728</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3821,25 +3821,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594475</v>
+        <v>594547</v>
       </c>
       <c r="R29" t="n">
-        <v>6843224</v>
+        <v>6843245</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3915,10 +3915,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121551311</v>
+        <v>121551257</v>
       </c>
       <c r="B30" t="n">
-        <v>80573</v>
+        <v>91411</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3927,25 +3927,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1049</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594277</v>
+        <v>594472</v>
       </c>
       <c r="R30" t="n">
-        <v>6843575</v>
+        <v>6843244</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121551257</v>
+        <v>121551311</v>
       </c>
       <c r="B31" t="n">
-        <v>91411</v>
+        <v>80573</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4033,25 +4033,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>1049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594472</v>
+        <v>594277</v>
       </c>
       <c r="R31" t="n">
-        <v>6843244</v>
+        <v>6843575</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -2961,10 +2961,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121551304</v>
+        <v>121551329</v>
       </c>
       <c r="B21" t="n">
-        <v>74661</v>
+        <v>88046</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2973,25 +2973,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594300</v>
+        <v>594316</v>
       </c>
       <c r="R21" t="n">
-        <v>6843515</v>
+        <v>6843272</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3067,7 +3067,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121551276</v>
+        <v>121551293</v>
       </c>
       <c r="B22" t="n">
         <v>90728</v>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594521</v>
+        <v>594547</v>
       </c>
       <c r="R22" t="n">
-        <v>6843232</v>
+        <v>6843245</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3173,10 +3173,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121551295</v>
+        <v>121551257</v>
       </c>
       <c r="B23" t="n">
-        <v>91014</v>
+        <v>91411</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3185,25 +3185,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594430</v>
+        <v>594472</v>
       </c>
       <c r="R23" t="n">
-        <v>6843483</v>
+        <v>6843244</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121551326</v>
+        <v>121551276</v>
       </c>
       <c r="B24" t="n">
-        <v>90748</v>
+        <v>90728</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594341</v>
+        <v>594521</v>
       </c>
       <c r="R24" t="n">
-        <v>6843401</v>
+        <v>6843232</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121551329</v>
+        <v>121551250</v>
       </c>
       <c r="B25" t="n">
-        <v>88046</v>
+        <v>90739</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3397,25 +3397,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>1205</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594316</v>
+        <v>594475</v>
       </c>
       <c r="R25" t="n">
-        <v>6843272</v>
+        <v>6843224</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121551250</v>
+        <v>121551326</v>
       </c>
       <c r="B27" t="n">
-        <v>90739</v>
+        <v>90748</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3609,25 +3609,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1205</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594475</v>
+        <v>594341</v>
       </c>
       <c r="R27" t="n">
-        <v>6843224</v>
+        <v>6843401</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121551293</v>
+        <v>121551304</v>
       </c>
       <c r="B29" t="n">
-        <v>90728</v>
+        <v>74661</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3821,25 +3821,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594547</v>
+        <v>594300</v>
       </c>
       <c r="R29" t="n">
-        <v>6843245</v>
+        <v>6843515</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3915,10 +3915,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121551257</v>
+        <v>121551311</v>
       </c>
       <c r="B30" t="n">
-        <v>91411</v>
+        <v>80573</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3927,25 +3927,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>1049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594472</v>
+        <v>594277</v>
       </c>
       <c r="R30" t="n">
-        <v>6843244</v>
+        <v>6843575</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121551311</v>
+        <v>121551295</v>
       </c>
       <c r="B31" t="n">
-        <v>80573</v>
+        <v>91014</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594277</v>
+        <v>594430</v>
       </c>
       <c r="R31" t="n">
-        <v>6843575</v>
+        <v>6843483</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -2961,10 +2961,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121551329</v>
+        <v>121551311</v>
       </c>
       <c r="B21" t="n">
-        <v>88046</v>
+        <v>80573</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594316</v>
+        <v>594277</v>
       </c>
       <c r="R21" t="n">
-        <v>6843272</v>
+        <v>6843575</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121551293</v>
+        <v>121551250</v>
       </c>
       <c r="B22" t="n">
-        <v>90728</v>
+        <v>90739</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3079,25 +3079,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594547</v>
+        <v>594475</v>
       </c>
       <c r="R22" t="n">
-        <v>6843245</v>
+        <v>6843224</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3173,10 +3173,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121551257</v>
+        <v>121551321</v>
       </c>
       <c r="B23" t="n">
-        <v>91411</v>
+        <v>91014</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3185,25 +3185,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594472</v>
+        <v>594291</v>
       </c>
       <c r="R23" t="n">
-        <v>6843244</v>
+        <v>6843558</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121551276</v>
+        <v>121551304</v>
       </c>
       <c r="B24" t="n">
-        <v>90728</v>
+        <v>74661</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3291,25 +3291,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594521</v>
+        <v>594300</v>
       </c>
       <c r="R24" t="n">
-        <v>6843232</v>
+        <v>6843515</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121551250</v>
+        <v>121551326</v>
       </c>
       <c r="B25" t="n">
-        <v>90739</v>
+        <v>90748</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3397,25 +3397,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1205</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594475</v>
+        <v>594341</v>
       </c>
       <c r="R25" t="n">
-        <v>6843224</v>
+        <v>6843401</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,10 +3491,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121551321</v>
+        <v>121551329</v>
       </c>
       <c r="B26" t="n">
-        <v>91014</v>
+        <v>88046</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3507,21 +3507,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594291</v>
+        <v>594316</v>
       </c>
       <c r="R26" t="n">
-        <v>6843558</v>
+        <v>6843272</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121551326</v>
+        <v>121551257</v>
       </c>
       <c r="B27" t="n">
-        <v>90748</v>
+        <v>91411</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3609,25 +3609,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594341</v>
+        <v>594472</v>
       </c>
       <c r="R27" t="n">
-        <v>6843401</v>
+        <v>6843244</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121551304</v>
+        <v>121551293</v>
       </c>
       <c r="B29" t="n">
-        <v>74661</v>
+        <v>90728</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3821,25 +3821,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594300</v>
+        <v>594547</v>
       </c>
       <c r="R29" t="n">
-        <v>6843515</v>
+        <v>6843245</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3915,10 +3915,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121551311</v>
+        <v>121551276</v>
       </c>
       <c r="B30" t="n">
-        <v>80573</v>
+        <v>90728</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3931,21 +3931,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594277</v>
+        <v>594521</v>
       </c>
       <c r="R30" t="n">
-        <v>6843575</v>
+        <v>6843232</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -2961,10 +2961,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121551311</v>
+        <v>121551326</v>
       </c>
       <c r="B21" t="n">
-        <v>80573</v>
+        <v>90748</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594277</v>
+        <v>594341</v>
       </c>
       <c r="R21" t="n">
-        <v>6843575</v>
+        <v>6843401</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121551250</v>
+        <v>121551293</v>
       </c>
       <c r="B22" t="n">
-        <v>90739</v>
+        <v>90728</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3079,25 +3079,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594475</v>
+        <v>594547</v>
       </c>
       <c r="R22" t="n">
-        <v>6843224</v>
+        <v>6843245</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3166,17 +3166,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121551321</v>
+        <v>121551297</v>
       </c>
       <c r="B23" t="n">
-        <v>91014</v>
+        <v>88046</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3189,21 +3189,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594291</v>
+        <v>594431</v>
       </c>
       <c r="R23" t="n">
-        <v>6843558</v>
+        <v>6843482</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3272,17 +3272,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121551304</v>
+        <v>121551257</v>
       </c>
       <c r="B24" t="n">
-        <v>74661</v>
+        <v>91411</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594300</v>
+        <v>594472</v>
       </c>
       <c r="R24" t="n">
-        <v>6843515</v>
+        <v>6843244</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3378,17 +3378,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121551326</v>
+        <v>121551295</v>
       </c>
       <c r="B25" t="n">
-        <v>90748</v>
+        <v>91014</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3401,21 +3401,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594341</v>
+        <v>594430</v>
       </c>
       <c r="R25" t="n">
-        <v>6843401</v>
+        <v>6843483</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121551257</v>
+        <v>121551304</v>
       </c>
       <c r="B27" t="n">
-        <v>91411</v>
+        <v>74661</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594472</v>
+        <v>594300</v>
       </c>
       <c r="R27" t="n">
-        <v>6843244</v>
+        <v>6843515</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3696,17 +3696,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121551297</v>
+        <v>121551250</v>
       </c>
       <c r="B28" t="n">
-        <v>88046</v>
+        <v>90739</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3715,25 +3715,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>1205</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594431</v>
+        <v>594475</v>
       </c>
       <c r="R28" t="n">
-        <v>6843482</v>
+        <v>6843224</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3802,14 +3802,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121551293</v>
+        <v>121551276</v>
       </c>
       <c r="B29" t="n">
         <v>90728</v>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594547</v>
+        <v>594521</v>
       </c>
       <c r="R29" t="n">
-        <v>6843245</v>
+        <v>6843232</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3908,17 +3908,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121551276</v>
+        <v>121551311</v>
       </c>
       <c r="B30" t="n">
-        <v>90728</v>
+        <v>80573</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3931,21 +3931,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594521</v>
+        <v>594277</v>
       </c>
       <c r="R30" t="n">
-        <v>6843232</v>
+        <v>6843575</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4014,14 +4014,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121551295</v>
+        <v>121551321</v>
       </c>
       <c r="B31" t="n">
         <v>91014</v>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594430</v>
+        <v>594291</v>
       </c>
       <c r="R31" t="n">
-        <v>6843483</v>
+        <v>6843558</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 8671-2022 artfynd.xlsx
+++ b/artfynd/A 8671-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63434549</v>
+        <v>63434546</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>392</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ofärnebrättingen, V om, Hls</t>
+          <t>Ofärnebrättingens västsida, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594348.9429175189</v>
+        <v>594327</v>
       </c>
       <c r="R2" t="n">
-        <v>6843236.877230193</v>
+        <v>6843591</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,21 +743,11 @@
           <t>2017-01-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-01-31</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,15 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>grannaturskog i bäckmiljö</t>
+          <t>sydvänd, ljus barrnaturskog</t>
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga</t>
+          <t>2 substratenheter # gammal asp</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,53 +785,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63434544</v>
+        <v>121455780</v>
       </c>
       <c r="B3" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ofärnebrättingens SV-sida, Hls</t>
+          <t>Vallabrättingens sydsida, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594358.0101061902</v>
+        <v>594412</v>
       </c>
       <c r="R3" t="n">
-        <v>6843529.86915154</v>
+        <v>6843245</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +869,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>barrnaturskog</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN3" t="n">
@@ -907,7 +877,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga</t>
+          <t>1 substratenheter # förrötad klenare granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -918,22 +888,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63434543</v>
+        <v>121551297</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,37 +906,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ofärnebrättingens V-sida, Hls</t>
+          <t>Ofärnebrättingen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594350.9661193405</v>
+        <v>594431</v>
       </c>
       <c r="R4" t="n">
-        <v>6843526.829208151</v>
+        <v>6843482</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,22 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,84 +977,70 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>barrnaturskog i kant mot kärr</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>2 substratenheter # granlågor</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>63434541</v>
+        <v>121551329</v>
       </c>
       <c r="B5" t="n">
-        <v>89794</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5321</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ofärnebrättingens SV-sida, Hls</t>
+          <t>Ofärnebrättingen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594430.2008286007</v>
+        <v>594316</v>
       </c>
       <c r="R5" t="n">
-        <v>6843479.187421675</v>
+        <v>6843272</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,22 +1064,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,81 +1078,64 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>gammal asprik barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter # asplåga med barken kvar</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>63434545</v>
+        <v>63434537</v>
       </c>
       <c r="B6" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ofärnebrättingens västsida, Hls</t>
+          <t>Ofärnebrättingens sydvästsida, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594369.9644073867</v>
+        <v>594490</v>
       </c>
       <c r="R6" t="n">
-        <v>6843579.064407385</v>
+        <v>6843498</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1248,21 +1165,11 @@
           <t>2017-01-31</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-01-31</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1274,7 +1181,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>sydvästvänd barrnaturskog</t>
+          <t>hänglavsrik gammal grannaturskog</t>
         </is>
       </c>
       <c r="AN6" t="n">
@@ -1282,7 +1189,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # asp, gammal och grov</t>
+          <t>1 substratenheter # granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1300,50 +1207,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>63434546</v>
+        <v>63434542</v>
       </c>
       <c r="B7" t="n">
-        <v>78479</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>392</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ofärnebrättingens västsida, Hls</t>
+          <t>Ofärnebrättingens SV-sida, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594326.868631481</v>
+        <v>594394</v>
       </c>
       <c r="R7" t="n">
-        <v>6843591.166054305</v>
+        <v>6843495</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1373,21 +1275,11 @@
           <t>2017-01-31</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-01-31</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1399,7 +1291,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>sydvänd, ljus barrnaturskog</t>
+          <t>asprik barrnaturskog</t>
         </is>
       </c>
       <c r="AN7" t="n">
@@ -1407,7 +1299,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2 substratenheter # gammal asp</t>
+          <t>2 substratenheter # granlågor av gamla granar</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1425,15 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>63434542</v>
+        <v>121455777</v>
       </c>
       <c r="B8" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,28 +1337,28 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ofärnebrättingens SV-sida, Hls</t>
+          <t>Vallabrättingens sydsida, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594394.1345928371</v>
+        <v>594291</v>
       </c>
       <c r="R8" t="n">
-        <v>6843494.802853245</v>
+        <v>6843506</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1495,22 +1382,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,7 +1401,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>asprik barrnaturskog</t>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN8" t="n">
@@ -1532,7 +1409,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>2 substratenheter # granlågor av gamla granar</t>
+          <t>2 substratenheter # förrötade grövre granlågor</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1543,22 +1420,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>63434539</v>
+        <v>121455778</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,37 +1438,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ofärnebrättingens SV-sida, Hls</t>
+          <t>Vallabrättingens sydsida, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594468.906680025</v>
+        <v>594430</v>
       </c>
       <c r="R9" t="n">
-        <v>6843505.870772809</v>
+        <v>6843492</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1620,22 +1492,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1649,15 +1511,15 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>gammal grannaturskog</t>
+          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN9" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>100 substratenheter # gamla granar</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1668,22 +1530,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>63434540</v>
+        <v>121455781</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,37 +1548,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ofärnebrättingens SV-sida, Hls</t>
+          <t>Vallabrättingens sydsida, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594437.1285355991</v>
+        <v>594412</v>
       </c>
       <c r="R10" t="n">
-        <v>6843451.859486742</v>
+        <v>6843245</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1745,22 +1602,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,15 +1621,15 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>gammal barrnaturskog</t>
+          <t>relativt gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>4 substratenheter # granlågor av gamla granar</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1793,22 +1640,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>63434547</v>
+        <v>121551295</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,37 +1658,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ofärnebrättingens västsida, Hls</t>
+          <t>Ofärnebrättingen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594324.8654144527</v>
+        <v>594430</v>
       </c>
       <c r="R11" t="n">
-        <v>6843594.906565286</v>
+        <v>6843483</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1870,22 +1715,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1894,46 +1729,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AN11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>3 substratenheter # granlågor</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121455777</v>
+        <v>121551321</v>
       </c>
       <c r="B12" t="n">
-        <v>91014</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1950,25 +1768,28 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vallabrättingens sydsida, Hls</t>
+          <t>Ofärnebrättingen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>594291</v>
       </c>
       <c r="R12" t="n">
-        <v>6843506</v>
+        <v>6843558</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2009,81 +1830,67 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
-        </is>
-      </c>
-      <c r="AN12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>2 substratenheter # förrötade grövre granlågor</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121455782</v>
+        <v>121551311</v>
       </c>
       <c r="B13" t="n">
-        <v>91168</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vallabrättingens sydsida, Hls</t>
+          <t>Ofärnebrättingen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594412</v>
+        <v>594277</v>
       </c>
       <c r="R13" t="n">
-        <v>6843245</v>
+        <v>6843575</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2124,46 +1931,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
-        </is>
-      </c>
-      <c r="AN13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121455780</v>
+        <v>63434540</v>
       </c>
       <c r="B14" t="n">
-        <v>88046</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2171,37 +1961,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vallabrättingens sydsida, Hls</t>
+          <t>Ofärnebrättingens SV-sida, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594412</v>
+        <v>594437</v>
       </c>
       <c r="R14" t="n">
-        <v>6843245</v>
+        <v>6843452</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2225,12 +2015,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2244,15 +2034,15 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AN14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad klenare granlåga</t>
+          <t>4 substratenheter # granlågor av gamla granar</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2263,22 +2053,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121455779</v>
+        <v>63434543</v>
       </c>
       <c r="B15" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,17 +2091,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vallabrättingens sydsida, Hls</t>
+          <t>Ofärnebrättingens V-sida, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594435</v>
+        <v>594351</v>
       </c>
       <c r="R15" t="n">
-        <v>6843227</v>
+        <v>6843527</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2340,12 +2125,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2359,15 +2144,15 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>gammal barrnaturskog i sydsida</t>
+          <t>barrnaturskog i kant mot kärr</t>
         </is>
       </c>
       <c r="AN15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>2 substratenheter # granlågor</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2378,22 +2163,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121455775</v>
+        <v>63434547</v>
       </c>
       <c r="B16" t="n">
-        <v>90748</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2401,37 +2181,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vallabrättingens sydsida, Hls</t>
+          <t>Ofärnebrättingens västsida, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594314</v>
+        <v>594325</v>
       </c>
       <c r="R16" t="n">
-        <v>6843411</v>
+        <v>6843595</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2455,12 +2235,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2469,21 +2249,20 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>bergskrön med gammal hällmarkstallskog</t>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AN16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>1 substratenheter # 400-årig tall med stamsår</t>
+          <t>3 substratenheter # granlågor</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2494,22 +2273,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121455778</v>
+        <v>63434549</v>
       </c>
       <c r="B17" t="n">
-        <v>91014</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,37 +2291,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vallabrättingens sydsida, Hls</t>
+          <t>Ofärnebrättingen, V om, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594430</v>
+        <v>594349</v>
       </c>
       <c r="R17" t="n">
-        <v>6843492</v>
+        <v>6843237</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2571,12 +2345,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2590,7 +2364,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i terrängsvacka</t>
+          <t>grannaturskog i bäckmiljö</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -2598,7 +2372,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>1 substratenheter # granlåga</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2609,22 +2383,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121455781</v>
+        <v>121455776</v>
       </c>
       <c r="B18" t="n">
-        <v>91014</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,21 +2401,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2656,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594412</v>
+        <v>594238</v>
       </c>
       <c r="R18" t="n">
-        <v>6843245</v>
+        <v>6843576</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2705,15 +2474,15 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog i sydsida</t>
+          <t>relativt gammal grannaturskog i terrängsvacka</t>
         </is>
       </c>
       <c r="AN18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>2 substratenheter # förrötade äldre granlågor</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2731,15 +2500,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121455774</v>
+        <v>121455779</v>
       </c>
       <c r="B19" t="n">
-        <v>79152</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2747,21 +2511,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1352</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2771,10 +2535,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594327</v>
+        <v>594435</v>
       </c>
       <c r="R19" t="n">
-        <v>6843367</v>
+        <v>6843227</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2820,7 +2584,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
+          <t>gammal barrnaturskog i sydsida</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -2828,7 +2592,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>1 substratenheter # grenar på fallen äldre asp</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2846,15 +2610,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121455776</v>
+        <v>121551276</v>
       </c>
       <c r="B20" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,16 +2639,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vallabrättingens sydsida, Hls</t>
+          <t>Ofärnebrättingen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594238</v>
+        <v>594521</v>
       </c>
       <c r="R20" t="n">
-        <v>6843576</v>
+        <v>6843232</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2930,46 +2692,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>relativt gammal grannaturskog i terrängsvacka</t>
-        </is>
-      </c>
-      <c r="AN20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>2 substratenheter # förrötade äldre granlågor</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121551326</v>
+        <v>121551293</v>
       </c>
       <c r="B21" t="n">
-        <v>90748</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2977,21 +2722,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3004,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594341</v>
+        <v>594547</v>
       </c>
       <c r="R21" t="n">
-        <v>6843401</v>
+        <v>6843245</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3067,56 +2812,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121551293</v>
+        <v>63434548</v>
       </c>
       <c r="B22" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ofärnebrättingen, Hls</t>
+          <t>Ofärnebrättingen, S om, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594547</v>
+        <v>594385</v>
       </c>
       <c r="R22" t="n">
-        <v>6843245</v>
+        <v>6843214</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3140,12 +2877,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3154,56 +2891,63 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>skiitad granskog med gamla träd vid bäck</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal granlåga</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Per-Gunnar Jacobsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121551297</v>
+        <v>121551250</v>
       </c>
       <c r="B23" t="n">
-        <v>88046</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>1205</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3216,10 +2960,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594431</v>
+        <v>594475</v>
       </c>
       <c r="R23" t="n">
-        <v>6843482</v>
+        <v>6843224</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3272,63 +3016,55 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121551257</v>
+        <v>63434544</v>
       </c>
       <c r="B24" t="n">
-        <v>91411</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ofärnebrättingen, Hls</t>
+          <t>Ofärnebrättingens SV-sida, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594472</v>
+        <v>594358</v>
       </c>
       <c r="R24" t="n">
-        <v>6843244</v>
+        <v>6843530</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3352,12 +3088,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3366,34 +3102,41 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>1 substratenheter # granlåga</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Per-Gunnar Jacobsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121551295</v>
+        <v>121455782</v>
       </c>
       <c r="B25" t="n">
-        <v>91014</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,37 +3144,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ofärnebrättingen, Hls</t>
+          <t>Vallabrättingens sydsida, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594430</v>
+        <v>594412</v>
       </c>
       <c r="R25" t="n">
-        <v>6843483</v>
+        <v>6843245</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3472,14 +3212,26 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>relativt gammal barrnaturskog i sydsida</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Per-Gunnar Jacobsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3491,15 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121551329</v>
+        <v>121455774</v>
       </c>
       <c r="B26" t="n">
-        <v>88046</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3507,37 +3254,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>1352</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ofärnebrättingen, Hls</t>
+          <t>Vallabrättingens sydsida, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594316</v>
+        <v>594327</v>
       </c>
       <c r="R26" t="n">
-        <v>6843272</v>
+        <v>6843367</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3578,34 +3322,41 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>relativt gammal asprik grannaturskog i sydsluttning</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grenar på fallen äldre asp</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Per-Gunnar Jacobsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
+          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121551304</v>
+        <v>121551257</v>
       </c>
       <c r="B27" t="n">
-        <v>74661</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3613,21 +3364,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3640,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594300</v>
+        <v>594472</v>
       </c>
       <c r="R27" t="n">
-        <v>6843515</v>
+        <v>6843244</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3696,22 +3447,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121551250</v>
+        <v>63434541</v>
       </c>
       <c r="B28" t="n">
-        <v>90739</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,40 +3465,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1205</v>
+        <v>5321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ofärnebrättingen, Hls</t>
+          <t>Ofärnebrättingens SV-sida, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594475</v>
+        <v>594430</v>
       </c>
       <c r="R28" t="n">
-        <v>6843224</v>
+        <v>6843479</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3776,12 +3519,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3790,34 +3533,41 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>gammal asprik barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>1 substratenheter # asplåga med barken kvar</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Per-Gunnar Jacobsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121551276</v>
+        <v>121455775</v>
       </c>
       <c r="B29" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3825,37 +3575,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ofärnebrättingen, Hls</t>
+          <t>Vallabrättingens sydsida, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594521</v>
+        <v>594314</v>
       </c>
       <c r="R29" t="n">
-        <v>6843232</v>
+        <v>6843411</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3900,10 +3647,23 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>bergskrön med gammal hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>1 substratenheter # 400-årig tall med stamsår</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Per-Gunnar Jacobsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -3915,15 +3675,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121551311</v>
+        <v>121551326</v>
       </c>
       <c r="B30" t="n">
-        <v>80573</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,21 +3686,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1049</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3958,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594277</v>
+        <v>594341</v>
       </c>
       <c r="R30" t="n">
-        <v>6843575</v>
+        <v>6843401</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4014,63 +3769,55 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Andersson, Per-Gunnar Jacobsson</t>
+          <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121551321</v>
+        <v>63434539</v>
       </c>
       <c r="B31" t="n">
-        <v>91014</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ofärnebrättingen, Hls</t>
+          <t>Ofärnebrättingens SV-sida, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594291</v>
+        <v>594469</v>
       </c>
       <c r="R31" t="n">
-        <v>6843558</v>
+        <v>6843506</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4094,12 +3841,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4108,22 +3855,355 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>gammal grannaturskog</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>100 substratenheter # gamla granar</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121551304</v>
+      </c>
+      <c r="B32" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ofärnebrättingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>594300</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6843515</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
           <t>Per-Gunnar Jacobsson</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
+      <c r="AX32" t="inlineStr">
         <is>
           <t>Per-Gunnar Jacobsson, Magnus Andersson</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>63434538</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ofärnebrättingens västsida, Hls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>594499</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6843480</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2017-01-31</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2017-01-31</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>hänglavsrik barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>1 substratenheter # högstubbe av gammal asp</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>63434545</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ofärnebrättingens västsida, Hls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>594370</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6843579</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2017-01-31</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2017-01-31</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>sydvästvänd barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>1 substratenheter # asp, gammal och grov</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
